--- a/StructureDefinition-ncpi-research-access-policy.xlsx
+++ b/StructureDefinition-ncpi-research-access-policy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -364,7 +364,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -607,7 +607,7 @@
     <t>The four anticipated uses for the Consent Resource.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-scope</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-scope|4.0.1</t>
   </si>
   <si>
     <t>Consent.category</t>
@@ -631,7 +631,7 @@
     <t>A classification of the type of consents found in a consent statement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-category</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-category|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -649,7 +649,7 @@
     <t>Consent.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -706,7 +706,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -735,7 +735,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -752,7 +752,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|DocumentReference|Contract|QuestionnaireResponse)</t>
+Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
   </si>
   <si>
     <t>Source from which this consent is taken</t>
@@ -868,7 +868,7 @@
     <t>Regulatory policy examples.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-policy</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-policy|4.0.1</t>
   </si>
   <si>
     <t>Consent.verification</t>
@@ -905,7 +905,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -1019,13 +1019,13 @@
     <t>How an actor is involved in the consent considerations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-role-type</t>
+    <t>http://hl7.org/fhir/ValueSet/security-role-type|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Group|CareTeam|Organization|Patient|Practitioner|RelatedPerson|PractitionerRole)
+    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1056,7 +1056,7 @@
     <t>Detailed codes for the consent action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-action</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-action|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.securityLabel</t>
@@ -1078,7 +1078,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.purpose</t>
@@ -1111,7 +1111,7 @@
     <t>The class (type) of information a consent rule covers.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-class</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-class|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.code</t>
@@ -1129,7 +1129,7 @@
     <t>If this code is found in an instance, then the exception applies.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/consent-content-code</t>
+    <t>http://hl7.org/fhir/ValueSet/consent-content-code|4.0.1</t>
   </si>
   <si>
     <t>Consent.provision.dataPeriod</t>
@@ -1183,7 +1183,7 @@
     <t>Consent.provision.data.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1514,7 +1514,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.8359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-research-access-policy.xlsx
+++ b/StructureDefinition-ncpi-research-access-policy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -488,7 +488,7 @@
     <t>website</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/research-web-Link}
+    <t xml:space="preserve">Extension {https://nih-ncpi.github.io/ncpi-fhir-ig-2/StructureDefinition/research-web-link}
 </t>
   </si>
   <si>

--- a/StructureDefinition-ncpi-research-access-policy.xlsx
+++ b/StructureDefinition-ncpi-research-access-policy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-research-access-policy.xlsx
+++ b/StructureDefinition-ncpi-research-access-policy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-research-access-policy.xlsx
+++ b/StructureDefinition-ncpi-research-access-policy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
